--- a/data/CompraSanJose.xlsx
+++ b/data/CompraSanJose.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,7 +808,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.44 kg</t>
+          <t>7.91 kg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12 ud</t>
+          <t>16 ud</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.72 kg</t>
+          <t>4.18 kg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alitas de pollo</t>
+          <t>Aguja de vaca</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4 kg</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Costillas de cerdo</t>
+          <t>Carrillera de ternera</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.71 kg</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entrecot de vaca</t>
+          <t>Chuletas de cordero</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>930</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.02 kg</t>
+          <t>930 g</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Filetes de ternera</t>
+          <t>Chuleton de buey</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.79 kg</t>
+          <t>1.08 kg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lomo de cerdo</t>
+          <t>Entrecot de vaca</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>1.55 kg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pinchitos</t>
+          <t>Filetes de ternera</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.08 kg</t>
+          <t>2.79 kg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pollo en tiras</t>
+          <t>Lomo de cerdo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.33 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pollo troceado</t>
+          <t>Pinchitos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>620</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.07 kg</t>
+          <t>620 g</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1524,17 +1524,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Pluma de cerdo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>620</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>465 g</t>
+          <t>620 g</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chistorra</t>
+          <t>Pollo en tiras</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>620 g</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1590,17 +1590,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Pollo troceado</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.86 kg</t>
+          <t>5.42 kg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1623,12 +1623,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chorizo parrilla</t>
+          <t>Presa de cerdo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1656,17 +1656,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jamon cocido</t>
+          <t>Secreto de cerdo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>775</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>465 g</t>
+          <t>775 g</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jamon serrano</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>542.5</t>
+          <t>465</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>542.5 g</t>
+          <t>465 g</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longaniza</t>
+          <t>Chistorra</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>465</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>775 g</t>
+          <t>465 g</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Morcilla</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>1.86 kg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Panceta</t>
+          <t>Chorizo parrilla</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>930</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>930 g</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Salami/pepperoni</t>
+          <t>Jamon cocido</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>387.5</t>
+          <t>465</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>387.5 g</t>
+          <t>465 g</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1854,17 +1854,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Boquerones</t>
+          <t>Jamon serrano</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>542.5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>542.5 g</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Calamar</t>
+          <t>Longaniza</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>775</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>775 g</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1920,12 +1920,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cazon</t>
+          <t>Morcilla</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rosada</t>
+          <t>Panceta</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.08 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1986,17 +1986,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Masa de pizza</t>
+          <t>Salami/pepperoni</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>387.5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2.33 kg</t>
+          <t>387.5 g</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Almejas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>775</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.41 kg</t>
+          <t>775 g</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2052,27 +2052,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pan de hamburguesa</t>
+          <t>Boquerones</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24 ud</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pan del dia anterior</t>
+          <t>Calamar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.86 kg</t>
+          <t>2.17 kg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2118,27 +2118,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tortillas de trigo</t>
+          <t>Cazon</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31 ud</t>
+          <t>1.08 kg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2151,27 +2151,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Huevo</t>
+          <t>Gambas/langostinos</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>59 ud</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2184,27 +2184,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Leche</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.33 L</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mantequilla</t>
+          <t>Rosada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>232.5 g</t>
+          <t>1.08 kg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2250,17 +2250,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mozzarella</t>
+          <t>Masa de pizza</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nata agria</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>465 g</t>
+          <t>3.41 kg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2316,27 +2316,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Queso en lonchas</t>
+          <t>Pan de hamburguesa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>310 g</t>
+          <t>24 ud</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2349,17 +2349,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Queso rallado</t>
+          <t>Pan del dia anterior</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>852.5</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>852.5 g</t>
+          <t>1.86 kg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2382,27 +2382,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Congelados</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Guisantes</t>
+          <t>Tortillas de trigo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>465 g</t>
+          <t>31 ud</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2415,27 +2415,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Congelados</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Patatas congeladas</t>
+          <t>Huevo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2.33 kg</t>
+          <t>59 ud</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2448,27 +2448,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aceitunas negras</t>
+          <t>Leche</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>232.5 g</t>
+          <t>2.33 L</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2481,17 +2481,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alubias rojas cocidas</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>232.5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.24 kg</t>
+          <t>232.5 g</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2514,17 +2514,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Arroz</t>
+          <t>Mozzarella</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.48 kg</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2547,27 +2547,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Caldo de carne</t>
+          <t>Nata agria</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>465</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>775 ml</t>
+          <t>465 g</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2580,27 +2580,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Caldo de pollo</t>
+          <t>Queso en lonchas</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6.2 L</t>
+          <t>310 g</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2613,17 +2613,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Garbanzos cocidos</t>
+          <t>Queso rallado</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>852.5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>775 g</t>
+          <t>852.5 g</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2646,17 +2646,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Congelados</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Guacamole</t>
+          <t>Guisantes</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>775</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>465 g</t>
+          <t>775 g</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2679,17 +2679,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Congelados</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lata de maiz</t>
+          <t>Patatas congeladas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>465 g</t>
+          <t>2.33 kg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pasas</t>
+          <t>Aceitunas negras</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pepinillos</t>
+          <t>Alubias rojas cocidas</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>232.5 g</t>
+          <t>1.24 kg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Semola couscous</t>
+          <t>Arroz</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4 kg</t>
+          <t>4.03 kg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2816,22 +2816,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tomate frito</t>
+          <t>Caldo de carne</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>775</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.86 kg</t>
+          <t>775 ml</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tomate natural</t>
+          <t>Caldo de pescado</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3.56 kg</t>
+          <t>3.88 L</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2882,30 +2882,360 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>Caldo de pollo</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>6.2 L</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Garbanzos cocidos</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>775 g</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Guacamole</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>465 g</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lata de maiz</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>465 g</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pasas</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>232.5</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>232.5 g</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pepinillos</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>232.5</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>232.5 g</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pimiento morron asado</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>465 g</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Semola couscous</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.4 kg</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tomate frito</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.86 kg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tomate natural</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4185</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>4.18 kg</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>Tomate tamizado</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>2.02 kg</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2918,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2944,6 +3274,11 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Notas</t>
         </is>
       </c>
@@ -2961,19 +3296,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paco</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1. Sofrie cebolla, pimientos y ajo en aceite.
-2. Dora el pollo troceado y el chorizo.
-3. Anade tomate natural y pimenton; rehoga.
-4. Incorpora el arroz y el caldo caliente (doble volumen).
-5. Anade guisantes; cuece 18 min y reposa 5 min.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>1. Pica pimiento verde, ajos y tomate. En la paellera, sofrie pimiento y ajos; anade la aguja de vaca troceada y el chorizo salpimentados y dora.
+2. Incorpora el tomate natural y rehoga.
+3. Anade el arroz (90-100 g/persona) y sofrielo 2 min con pimenton y colorante o azafran.
+4. Vierte el caldo caliente (3 veces el volumen de arroz) y cuece a fuego fuerte 8 min.
+5. Anade guisantes y el pimiento morron asado; baja a fuego minimo y cuece 8 min mas.
+6. Apaga, tapa con un pano y reposa 7-8 min.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-de-arroces/receta-arroz-campero-tipico-andalucia</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2993,14 +3334,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1. Lamina berenjena y patata; frie o asa.
-2. Sofrie cebolla y ajo; anade la ternera picada.
-3. Agrega tomate tamizado, vino y canela; reduce.
-4. Monta capas: patata, berenjena, carne.
-5. Cubre con bechamel (mantequilla, harina, leche, huevo, queso) y hornea 35 min a 190C.</t>
+          <t>1. Lamina las berenjenas, salalas y dejalas sudar; frielas ligeramente y reserva.
+2. Corta las patatas en rodajas y frielas ligeramente para la base.
+3. Pocha cebolla, anade tomate tamizado (nunca concentrado ni frito) y haz el sofrito.
+4. Incorpora la ternera picada dorada, un chorro de vino tinto y caldo; cuece 10 min hasta que no quede liquido.
+5. Prepara la bechamel (25 g mantequilla, 25 g harina, 500 ml leche) hasta que espese.
+6. Monta por capas: patata, berenjena, carne, berenjena; cubre con bechamel y queso.
+7. Hornea 20 min a 160C y gratina 3 min a 220C.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-de-carnes-y-aves/moussaka-receta-griega</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Con ternera (no cordero); tomate tamizado.</t>
         </is>
@@ -3024,14 +3372,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1. Sofrie cebolla, zanahoria (opcional), calabacin y pimiento.
-2. Anade el pollo y el ras el hanout.
-3. Incorpora tomate tamizado, garbanzos, pasas y caldo; guisa.
-4. Hidrata la semola con caldo caliente y aceite; desgrana.
-5. Sirve el guiso sobre el couscous.</t>
+          <t>1. Trocea la carrillera de ternera, salpimienta y dorala a fuego alto en la cazuela.
+2. Baja el fuego, anade cebolla y pocha 10 min.
+3. Incorpora muy poco tomate tamizado y cocina hasta evaporar.
+4. Anade caldo, la zanahoria en dados (opcional), jengibre, comino y curcuma; guisa a fuego lento hasta que la carne este muy tierna.
+5. Anade el calabacin y los garbanzos; cuece 10-15 min mas.
+6. Aparte, hidrata la semola con caldo hirviendo, tapa 5 min y desgrana con un tenedor.
+7. Sirve la semola de base y reparte el guiso por encima.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.todosacomer.net/recetas/guisos-pasta-arroces/cuscus-con-verduras-y-pollo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Zanahoria opcional; tomate tamizado (poco).</t>
         </is>
@@ -3055,14 +3410,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1. Frie las patatas en laminas a fuego medio hasta tiernas.
-2. Frie morcilla, chorizo, longaniza y lomo.
-3. Anade el jamon al final.
-4. Frie los huevos.
-5. Sirve todo junto con pimiento frito.</t>
+          <t>1. Corta las patatas en rodajas de 1/2 cm; pica ajo y corta cebolla y pimiento verde.
+2. En abundante aceite, frie ajo y luego patatas, cebolla y pimiento; 5 min a fuego fuerte.
+3. Baja el fuego y cocina 25 min removiendo hasta que las patatas a lo pobre esten tiernas; escurre y sala.
+4. Aparte, frie los embutidos (chorizo, morcilla, longaniza, lomo) 5 min; escurre.
+5. Frie los huevos en aceite muy caliente para que la puntilla quede crujiente.
+6. Emplata: base de patatas, encima embutidos, huevos fritos y unas lonchas de jamon.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
+        <is>
+          <t>https://bonviveur.com/es/recetas/plato-alpujarreno</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Patatas a lo pobre + embutido + huevos.</t>
         </is>
@@ -3086,14 +3447,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1. Tritura tomate, pan remojado, ajo y sal.
-2. Emulsiona anadiendo el AOVE en hilo.
-3. Ajusta con un poco de vinagre; enfria.
-4. Sirve con huevo duro y jamon picados.
-5. Acompana con los filetes a la plancha (o la opcion elegida).</t>
+          <t>1. Tritura los tomates (1 kg por cada 6 raciones); no hace falta pelar ni despepitar.
+2. Anade el pan (unos 200 g de telera por cada 6) y deja que se empape 10 min.
+3. Anade el ajo y tritura hasta una crema espesa.
+4. Incorpora el AOVE en hilo y bate hasta emulsionar; sala y enfria.
+5. Sirve frio con jamon picado y huevo cocido.
+6. De acompanamiento, salpimienta los filetes y hazlos a la plancha 2-3 min por cara.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-de-sopas-y-cremas/receta-de-salmorejo-cordobes-tradicional</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Acompanamiento elegible; por defecto filetes de ternera.</t>
         </is>
@@ -3117,14 +3484,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1. Humedece el pan troceado la noche antes.
-2. Frie ajos, chorizo y panceta; reserva.
-3. En esa grasa anade el pan y el pimenton.
-4. Remueve a fuego medio hasta que quede suelto y dorado.
-5. Sirve con los tropezones.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>1. Corta pan candeal asentado en cubos de 1 cm; humedecelo con agua salada, tapa con un pano y reposa (mejor de un dia para otro).
+2. Frie el chorizo en rodajas y la panceta en dados hasta que suelten grasa; reserva.
+3. En esa grasa, rehoga los ajos aplastados con piel 2-3 min sin quemar.
+4. Anade las migas de pan y el pimenton; cocina a fuego suave 10 min removiendo.
+5. Cuando esten sueltas y doradas, devuelve chorizo y panceta y mezcla.
+6. Para grupo grande, trabaja por tandas o en perol amplio; sirve muy caliente.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-tradicionales/mejor-receta-migas-pan-chorizo-clasico-potente-como-tradicional</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3144,14 +3517,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1. Sofrie cebolla, pimiento y ajo.
-2. Dora la carne picada.
-3. Anade comino, pimenton picante, tomate y caldo; guisa 30 min.
-4. Incorpora alubias y la lata de maiz; cuece 10 min.
-5. Sirve con arroz blanco.</t>
+          <t>1. Pocha la cebolla en aceite hasta transparente.
+2. Anade ajo, pimenton picante y comino; rehoga.
+3. Incorpora la carne picada y cocina hasta que pierda el color.
+4. Anade tomate, un poco de caldo y una pizca de azucar; cuece destapado 30 min.
+5. Anade las alubias rojas y la lata de maiz; cuece unos minutos.
+6. Rectifica de sal y picante; sirve con arroz blanco y nachos.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-de-carnes-y-aves/chili-receta-mexicana-con-y-sin-thermomix</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Con guarnicion de arroz.</t>
         </is>
@@ -3175,13 +3554,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1. Trocea el pollo y salpimienta.
-2. Coloca con patata y cebolla en bandeja.
-3. Riega con vino, aceite, limon y romero.
-4. Hornea 60-75 min a 200C regando de vez en cuando.</t>
+          <t>1. Precalienta el horno a 180C. Mezcla sal, pimienta y tomillo/romero.
+2. Parte las patatas, hazles cortes y colocalas en la bandeja engrasada.
+3. Sazona el pollo por dentro y fuera; introduce ajos en cortes y en la cavidad.
+4. Coloca el pollo sobre las patatas y hornea a 180C unos 45-60 min (remueve las patatas a media coccion).
+5. Pasa los jugos a un cazo, hierve y liga con un poco de maicena.
+6. Trincha, riega con la salsa y sirve; para mas comensales reparte en varias bandejas sin amontonar.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.hogarmania.com/cocina/recetas/carnes/pollo-asado-patatas-ensalada-verde-16651.html</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>El 'asado de carne/pescado'.</t>
         </is>
@@ -3205,13 +3591,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1. Pocha la cebolla y el pimiento verde en aceite.
-2. Anade el tomate frito; cuece 20 min a fuego lento.
-3. Sazona.
-4. Frie los huevos y sirvelos encima.</t>
+          <t>1. Pica en cuadraditos la cebolla y el pimiento verde; pica una pizca de ajo.
+2. Pocha cebolla, pimiento y ajo en aceite 10-15 min a fuego medio.
+3. Anade el tomate natural y cuece despacio hasta que quede meloso (no caldoso).
+4. Rectifica de sal (pizca de azucar si esta acido).
+5. Aparte, frie los huevos.
+6. Sirve el pisto con los huevos fritos por encima.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-de-legumbres-y-verduras/pisto-de-pimientos-y-tomates-la-receta-de-mi-abuela</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>RESPALDO: solo cebolla, tomate frito y pimiento verde + huevos.</t>
         </is>
@@ -3235,14 +3628,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1. Enciende las brasas con antelacion.
-2. Sala las carnes justo antes de asar.
-3. Asa primero lo que mas tarda (costillas).
-4. Anade embutidos y mazorcas.
-5. Sirve con pan y salsas.</t>
+          <t>1. Enciende la barbacoa 30-40 min antes; espera a que las brasas esten blanquecinas, sin llama.
+2. Reparte el carbon para calor uniforme; parrilla no muy pegada a las brasas.
+3. Empieza por el embutido y las piezas grasas: chorizo, panceta y morcilla.
+4. Asa la presa, el secreto y la pluma de cerdo a calor medio, girando cada pocos minutos.
+5. Haz los pinchitos dandoles vueltas para que se doren sin secarse.
+6. Usa carne fresca (sin congelar); retira cada pieza segun se dora.
+7. NO sales antes: echa la sal SOLO AL FINAL, en el plato.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/cultura-gastronomica/los-9-trucos-imprescindibles-para-convertirte-en-el-maestro-de-las-barbacoas</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Cerdo y embutido. Tope de carne por comensal (RF-26).</t>
         </is>
@@ -3266,14 +3666,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1. Enciende las brasas con antelacion.
-2. Sala las carnes justo antes de asar.
-3. Asa primero el entrecot y las alitas.
-4. Anade la verdura y las mazorcas.
-5. Sirve con pan y chimichurri.</t>
+          <t>1. Enciende las brasas 30-40 min antes; saca el vacuno de la nevera para atemperar.
+2. Sella el entrecot y el chuleton sobre brasa fuerte ~5 min por cara; una sola vuelta.
+3. Asa las chuletas de cordero hasta que esten doradas y jugosas.
+4. Haz la chistorra y el chorizo cerca del borde para que no revienten.
+5. Deja reposar el vacuno 5 min antes de trocear; acompana con chimichurri.
+6. Asa las verduras (calabacin, cebolleta, pimiento) y las mazorcas untadas de aceite, 5-10 min por lado.
+7. Echa la sal AL FINAL para no resecar la carne.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetario/83-mejores-recetas-barbacoa-para-sacar-todo-partido-a-parrilla-este-verano</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Vacuno, pollo y verdura. Tope de carne por comensal (RF-26).</t>
         </is>
@@ -3297,13 +3704,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1. Marca el pollo en tiras con las especias.
-2. Saltea con pimientos y cebolla.
-3. Calienta las tortillas.
-4. Monta con queso, guacamole, nata agria, tomate y lechuga.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>1. Corta el pollo en tiras y la cebolla y los pimientos en tiras anchas.
+2. Salpimienta el pollo y saltealo en aceite muy caliente; reserva.
+3. Saltea los pimientos y la cebolla hasta tiernos pero firmes.
+4. Devuelve el pollo, anade especias fajita (comino, pimenton) y un chorrito de lima.
+5. Calienta las tortillas en sarten seca por ambas caras.
+6. Rellena y enrolla; sirve con guacamole, nata agria, queso, tomate y lechuga.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.divinacocina.es/fajitas-de-pollo-faciles/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3319,14 +3733,21 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1. Forma las hamburguesas y salpimienta.
-2. Marca a la plancha al punto deseado.
-3. Tuesta el pan; funde el queso sobre la carne.
-4. Frie el bacon.
-5. Monta con lechuga, tomate, cebolla, pepinillos y salsas. Acompana con patatas.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>1. Usa carne picada fresca; salpimienta.
+2. Mezcla sin amasar en exceso y forma discos regulares.
+3. Deja reposar 10 min a temperatura ambiente.
+4. Plancha o parrilla a fuego medio-fuerte; coloca la hamburguesa untada de aceite.
+5. 2-3 min sin moverla; da la vuelta una vez y pon el queso encima; 2-4 min segun punto.
+6. Tuesta el pan por dentro.
+7. Monta: pan, lechuga y tomate, hamburguesa, bacon, cebolla y pepinillos, salsa y cierra. Acompana con patatas.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-de-carnes-y-aves/como-hacer-hamburguesas-caseras</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3342,14 +3763,21 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1. Estira la masa.
-2. Extiende el tomate.
-3. Reparte mozzarella y los ingredientes.
-4. Hornea a maxima temperatura 8-12 min.
-5. Oregano y aceite al salir.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>1. Mezcla la masa (harina, agua, levadura, sal, aceite) hasta homogenea; reposa 1-3 h.
+2. Divide, bolea y deja reposar; sacala 1-2 h antes si estaba en frio.
+3. Estira cada bola del centro a los bordes dejando el borde mas grueso.
+4. Precalienta el horno 45 min a la maxima temperatura (250C+).
+5. Extiende una capa fina de tomate, la mozzarella y los ingredientes sin sobrecargar.
+6. Hornea 3-4 min abajo y 3-4 min arriba, vigilando.
+7. Reposa unos minutos; anade oregano y aceite al salir.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.directoalpaladar.com/recetas-de-panes/pizza-casera-la-guia-definitiva</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3369,16 +3797,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1. Adoba el cazon (vinagre, pimenton, comino, ajo, oregano) unas horas.
-2. Limpia y trocea los pescados.
-3. Enharina con harina de freir/tempura.
-4. Frie en abundante aceite caliente por tandas.
-5. Sirve con limon.</t>
+          <t>1. Adobo del cazon: maja ajo, comino, oregano y pimenton, anade vinagre, laurel y sal.
+2. Corta el cazon en tacos, cubrelo con el adobo y macera en nevera 8 h (mejor toda la noche).
+3. Limpia y seca boquerones, calamar en anillas, rosada y el cazon escurrido.
+4. Enharina con harina de freir/tempura y sacude el exceso.
+5. Calienta abundante aceite a 180C sin que humee.
+6. Frie en tandas pequenas 30 s-2 min segun el pescado, una sola vuelta.
+7. Escurre en papel y sirve al momento con limon.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>https://www.directoalpaladar.com/recetas-de-aperitivos/como-se-hace-el-cazon-en-adobo-receta-de-bienmesabe</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Surtido elegible; incluye adobo y tempura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Almuerzo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paco</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1. Sofrie cebolla, pimiento y ajo en aceite; anade tomate natural.
+2. Rehoga el arroz con pimenton y azafran.
+3. Anade el caldo de pescado caliente (doble volumen) y los guisantes.
+4. Incorpora el calamar; a media coccion anade gambas, mejillones y almejas.
+5. Cuece 18 min sin remover; reposa 5 min. Sirve con limon.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Opcion alternativa de arroz.</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3656,12 +4123,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Aguja de vaca</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3679,12 +4146,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chorizo parrilla</t>
+          <t>Carrillera de ternera</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3702,12 +4169,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Morcilla</t>
+          <t>Presa de cerdo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3725,12 +4192,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Longaniza</t>
+          <t>Secreto de cerdo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3748,12 +4215,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Panceta</t>
+          <t>Pluma de cerdo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3771,12 +4238,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Chuleton de buey</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3794,12 +4261,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Salchichas</t>
+          <t>Chuletas de cordero</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charcuteria</t>
+          <t>Carniceria</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3817,7 +4284,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chistorra</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3840,7 +4307,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jamon serrano</t>
+          <t>Chorizo parrilla</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3863,7 +4330,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jamon cocido</t>
+          <t>Morcilla</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3886,7 +4353,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Salami/pepperoni</t>
+          <t>Longaniza</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3909,12 +4376,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Boquerones</t>
+          <t>Panceta</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3932,12 +4399,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Calamar</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3955,12 +4422,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rosada</t>
+          <t>Salchichas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3978,12 +4445,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cazon</t>
+          <t>Chistorra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pescaderia</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4001,12 +4468,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Berenjena</t>
+          <t>Jamon serrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4024,12 +4491,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Patata</t>
+          <t>Jamon cocido</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4047,12 +4514,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Salami/pepperoni</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Charcuteria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4070,12 +4537,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cebolleta</t>
+          <t>Boquerones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4093,12 +4560,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pimiento rojo</t>
+          <t>Calamar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4116,12 +4583,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pimiento verde</t>
+          <t>Rosada</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4139,12 +4606,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Zanahoria</t>
+          <t>Cazon</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4162,12 +4629,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Calabacin</t>
+          <t>Gambas/langostinos</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4185,12 +4652,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4208,12 +4675,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tomate maduro</t>
+          <t>Almejas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fruteria</t>
+          <t>Pescaderia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4231,7 +4698,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Berenjena</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4246,19 +4713,15 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Champinones</t>
+          <t>Patata</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4281,7 +4744,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lechuga</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4304,7 +4767,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Limon</t>
+          <t>Cebolleta</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4314,7 +4777,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4327,7 +4790,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mazorcas</t>
+          <t>Pimiento rojo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4337,7 +4800,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4350,7 +4813,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Perejil</t>
+          <t>Pimiento verde</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4373,12 +4836,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Zanahoria</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4396,12 +4859,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pan del dia anterior</t>
+          <t>Calabacin</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4419,17 +4882,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pan de hamburguesa</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4442,12 +4905,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Masa de pizza</t>
+          <t>Tomate maduro</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4465,40 +4928,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tortillas de trigo</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Panaderia</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Leche</t>
+          <t>Champinones</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4511,12 +4978,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mantequilla</t>
+          <t>Lechuga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4534,17 +5001,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Queso rallado</t>
+          <t>Limon</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4557,17 +5024,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mozzarella</t>
+          <t>Mazorcas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4580,12 +5047,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Queso en lonchas</t>
+          <t>Perejil</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Fruteria</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4603,12 +5070,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nata agria</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4626,17 +5093,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Huevo</t>
+          <t>Pan del dia anterior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lacteos</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4649,17 +5116,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Arroz</t>
+          <t>Pan de hamburguesa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4672,12 +5139,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Semola couscous</t>
+          <t>Masa de pizza</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4695,17 +5162,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Garbanzos cocidos</t>
+          <t>Tortillas de trigo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Panaderia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4718,17 +5185,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alubias rojas cocidas</t>
+          <t>Leche</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4741,12 +5208,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lata de maiz</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4764,12 +5231,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pasas</t>
+          <t>Queso rallado</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4787,17 +5254,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Caldo de pollo</t>
+          <t>Mozzarella</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4810,17 +5277,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Caldo de carne</t>
+          <t>Queso en lonchas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4833,12 +5300,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tomate natural</t>
+          <t>Nata agria</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4856,17 +5323,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tomate tamizado</t>
+          <t>Huevo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Despensa</t>
+          <t>Lacteos</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ud</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4879,7 +5346,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tomate frito</t>
+          <t>Arroz</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4902,7 +5369,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Guacamole</t>
+          <t>Semola couscous</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4925,7 +5392,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aceitunas negras</t>
+          <t>Garbanzos cocidos</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4948,7 +5415,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Pepinillos</t>
+          <t>Alubias rojas cocidas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4971,7 +5438,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Harina</t>
+          <t>Lata de maiz</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4986,19 +5453,15 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Harina de freir</t>
+          <t>Pasas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5013,19 +5476,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Caldo de pollo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5040,19 +5499,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AOVE</t>
+          <t>Caldo de carne</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5067,19 +5522,15 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aceite de girasol</t>
+          <t>Caldo de pescado</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5094,19 +5545,15 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vinagre</t>
+          <t>Azafran</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5116,7 +5563,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5133,7 +5580,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pimenton</t>
+          <t>Tomate natural</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5148,19 +5595,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pimenton picante</t>
+          <t>Tomate tamizado</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5175,19 +5618,15 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Comino</t>
+          <t>Tomate frito</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5202,19 +5641,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Guacamole</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5229,19 +5664,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Nuez moscada</t>
+          <t>Pimiento morron asado</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5256,19 +5687,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ras el hanout</t>
+          <t>Aceitunas negras</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5283,19 +5710,15 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Especias fajita</t>
+          <t>Pepinillos</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5310,19 +5733,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Oregano</t>
+          <t>Harina</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5349,7 +5768,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jengibre</t>
+          <t>Harina de freir</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5376,7 +5795,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Curcuma</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5386,7 +5805,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5403,7 +5822,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>AOVE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5413,7 +5832,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5430,7 +5849,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Aceite de girasol</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5440,7 +5859,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5457,7 +5876,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sal gorda</t>
+          <t>Vinagre</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5467,7 +5886,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5484,7 +5903,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sal de escamas</t>
+          <t>Pimenton</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5511,7 +5930,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Pimienta</t>
+          <t>Pimenton picante</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5538,7 +5957,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ketchup</t>
+          <t>Comino</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5565,7 +5984,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mostaza</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5592,7 +6011,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mayonesa</t>
+          <t>Nuez moscada</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5619,7 +6038,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alioli</t>
+          <t>Ras el hanout</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5646,7 +6065,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chimichurri</t>
+          <t>Especias fajita</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5673,17 +6092,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Vino tinto</t>
+          <t>Oregano</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Despensa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5700,17 +6119,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Vino blanco</t>
+          <t>Jengibre</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>Despensa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5727,12 +6146,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Guisantes</t>
+          <t>Curcuma</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Congelados</t>
+          <t>Despensa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5742,33 +6161,384 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>Romero</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sal gorda</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sal de escamas</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Pimienta</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ketchup</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Mostaza</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Mayonesa</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Alioli</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Chimichurri</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Despensa</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Vino tinto</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Vino blanco</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Bebidas</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guisantes</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Congelados</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>Patatas congeladas</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Congelados</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5781,7 +6551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5848,7 +6618,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pollo troceado</t>
+          <t>Aguja de vaca</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5872,7 +6642,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Pimiento morron asado</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5896,12 +6666,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pimiento rojo</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5920,7 +6690,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pimiento verde</t>
+          <t>Pimiento rojo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5944,7 +6714,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Pimiento verde</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5968,12 +6738,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomate natural</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -5992,12 +6762,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guisantes</t>
+          <t>Tomate natural</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -6016,12 +6786,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Guisantes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -6040,12 +6810,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caldo de pollo</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -6064,12 +6834,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Caldo de pollo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -6088,12 +6858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pimenton</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -6112,7 +6882,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Pimenton</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6131,17 +6901,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mousaka griega</t>
+          <t>Arroz campero</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Berenjena</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -6160,12 +6930,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Patata</t>
+          <t>Berenjena</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -6184,12 +6954,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carne picada de ternera</t>
+          <t>Patata</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6208,12 +6978,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Carne picada de ternera</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -6232,12 +7002,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tomate tamizado</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -6256,12 +7026,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Tomate tamizado</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -6280,12 +7050,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vino tinto</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -6304,12 +7074,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Leche</t>
+          <t>Vino tinto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -6328,12 +7098,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mantequilla</t>
+          <t>Leche</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -6352,7 +7122,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Harina</t>
+          <t>Mantequilla</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6376,12 +7146,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Queso rallado</t>
+          <t>Harina</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -6400,12 +7170,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huevo</t>
+          <t>Queso rallado</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -6424,12 +7194,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Huevo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -6448,12 +7218,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -6472,12 +7242,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nuez moscada</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -6496,12 +7266,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Nuez moscada</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6515,17 +7285,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Couscous</t>
+          <t>Mousaka griega</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Semola couscous</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -6544,12 +7314,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pollo troceado</t>
+          <t>Semola couscous</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6568,12 +7338,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Carrillera de ternera</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6592,7 +7362,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zanahoria</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6604,7 +7374,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6616,7 +7386,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Calabacin</t>
+          <t>Zanahoria</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6628,7 +7398,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -6640,12 +7410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Garbanzos cocidos</t>
+          <t>Calabacin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -6664,12 +7434,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tomate tamizado</t>
+          <t>Garbanzos cocidos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -6688,12 +7458,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pimiento rojo</t>
+          <t>Tomate tamizado</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -6712,12 +7482,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pasas</t>
+          <t>Pimiento rojo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -6736,12 +7506,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caldo de pollo</t>
+          <t>Pasas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -6760,12 +7530,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Caldo de pollo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -6784,12 +7554,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ras el hanout</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -6808,12 +7578,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Ras el hanout</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -6827,17 +7597,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Plato alpujarreno con huevos</t>
+          <t>Couscous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Patata</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -6856,12 +7626,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Morcilla</t>
+          <t>Patata</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -6880,7 +7650,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Morcilla</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6904,7 +7674,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longaniza</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6928,12 +7698,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lomo de cerdo</t>
+          <t>Longaniza</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -6952,12 +7722,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jamon serrano</t>
+          <t>Lomo de cerdo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -6976,12 +7746,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Huevo</t>
+          <t>Jamon serrano</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -7000,12 +7770,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pimiento verde</t>
+          <t>Huevo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -7024,12 +7794,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Pimiento verde</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -7048,12 +7818,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -7067,17 +7837,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salmorejo con acompanamiento</t>
+          <t>Plato alpujarreno con huevos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tomate maduro</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -7096,12 +7866,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Tomate maduro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -7120,12 +7890,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -7144,12 +7914,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AOVE</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -7168,12 +7938,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vinagre</t>
+          <t>AOVE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -7192,12 +7962,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Vinagre</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -7216,12 +7986,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Huevo</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -7240,12 +8010,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jamon serrano</t>
+          <t>Huevo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -7264,24 +8034,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Filetes de ternera</t>
+          <t>Jamon serrano</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Acompanamiento</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>No</t>
@@ -7291,21 +8053,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Migas</t>
+          <t>Salmorejo con acompanamiento</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pan del dia anterior</t>
+          <t>Filetes de ternera</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Acompanamiento</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>No</t>
@@ -7320,12 +8090,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chorizo</t>
+          <t>Pan del dia anterior</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -7344,7 +8114,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Panceta</t>
+          <t>Chorizo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7368,12 +8138,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Panceta</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -7392,12 +8162,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pimiento verde</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7416,12 +8186,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Pimiento verde</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -7440,12 +8210,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pimenton</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -7464,7 +8234,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Pimenton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7483,17 +8253,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Chili con carne</t>
+          <t>Migas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Carne picada de ternera</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7512,12 +8282,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Alubias rojas cocidas</t>
+          <t>Carne picada de ternera</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7536,12 +8306,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Alubias rojas cocidas</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -7560,12 +8330,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pimiento rojo</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -7584,12 +8354,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tomate natural</t>
+          <t>Pimiento rojo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7608,12 +8378,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Tomate natural</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -7632,12 +8402,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lata de maiz</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -7656,12 +8426,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Comino</t>
+          <t>Lata de maiz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7680,12 +8450,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pimenton picante</t>
+          <t>Comino</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -7704,12 +8474,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Caldo de carne</t>
+          <t>Pimenton picante</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -7728,12 +8498,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Caldo de carne</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -7752,12 +8522,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arroz</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -7776,12 +8546,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Arroz</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -7795,17 +8565,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Asado de pollo y patatas</t>
+          <t>Chili con carne</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pollo troceado</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -7824,12 +8594,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Patata</t>
+          <t>Pollo troceado</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -7848,12 +8618,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Patata</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -7872,12 +8642,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -7896,12 +8666,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Limon</t>
+          <t>Ajo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -7920,12 +8690,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vino blanco</t>
+          <t>Limon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7944,12 +8714,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Vino blanco</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7968,12 +8738,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7992,12 +8762,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8011,17 +8781,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pisto de verduras con huevos</t>
+          <t>Asado de pollo y patatas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -8040,7 +8810,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pimiento verde</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8064,12 +8834,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tomate frito</t>
+          <t>Pimiento verde</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -8088,12 +8858,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Huevo</t>
+          <t>Tomate frito</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -8112,12 +8882,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Huevo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -8136,12 +8906,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -8155,29 +8925,21 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Barbacoa 1</t>
+          <t>Pisto de verduras con huevos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Costillas de cerdo</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Carne</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>No</t>
@@ -8192,7 +8954,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pinchitos</t>
+          <t>Presa de cerdo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8224,12 +8986,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Chorizo parrilla</t>
+          <t>Secreto de cerdo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8239,7 +9001,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8256,7 +9018,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Panceta</t>
+          <t>Pluma de cerdo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8288,12 +9050,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Morcilla</t>
+          <t>Panceta</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8303,7 +9065,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8320,16 +9082,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mazorcas</t>
+          <t>Pinchitos</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>No</t>
@@ -8344,16 +9114,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Chorizo parrilla</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>No</t>
@@ -8368,16 +9146,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pimiento verde</t>
+          <t>Morcilla</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>No</t>
@@ -8392,12 +9178,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sal gorda</t>
+          <t>Mazorcas</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8416,12 +9202,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Alioli</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8435,29 +9221,21 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Barbacoa 2</t>
+          <t>Barbacoa 1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Entrecot de vaca</t>
+          <t>Pimiento verde</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Carne</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>No</t>
@@ -8467,29 +9245,21 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Barbacoa 2</t>
+          <t>Barbacoa 1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Alitas de pollo</t>
+          <t>Sal gorda</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Carne</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>No</t>
@@ -8499,29 +9269,21 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Barbacoa 2</t>
+          <t>Barbacoa 1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Chistorra</t>
+          <t>Alioli</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Carne</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>No</t>
@@ -8536,12 +9298,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Chorizo parrilla</t>
+          <t>Entrecot de vaca</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8551,7 +9313,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8568,16 +9330,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Calabacin</t>
+          <t>Chuleton de buey</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>No</t>
@@ -8592,16 +9362,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cebolleta</t>
+          <t>Chuletas de cordero</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>No</t>
@@ -8616,16 +9394,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pimiento rojo</t>
+          <t>Chistorra</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>No</t>
@@ -8640,16 +9426,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mazorcas</t>
+          <t>Chorizo parrilla</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>No</t>
@@ -8664,12 +9458,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Calabacin</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8688,12 +9482,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sal gorda</t>
+          <t>Cebolleta</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -8712,12 +9506,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Chimichurri</t>
+          <t>Pimiento rojo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -8731,17 +9525,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Fajitas</t>
+          <t>Barbacoa 2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pollo en tiras</t>
+          <t>Mazorcas</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -8755,17 +9549,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Fajitas</t>
+          <t>Barbacoa 2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tortillas de trigo</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -8779,17 +9573,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Fajitas</t>
+          <t>Barbacoa 2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Pimiento rojo</t>
+          <t>Sal gorda</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -8803,17 +9597,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Fajitas</t>
+          <t>Barbacoa 2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pimiento verde</t>
+          <t>Chimichurri</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -8832,12 +9626,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Pollo en tiras</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -8856,12 +9650,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Queso rallado</t>
+          <t>Tortillas de trigo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -8880,12 +9674,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nata agria</t>
+          <t>Pimiento rojo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -8904,12 +9698,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Pimiento verde</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -8928,12 +9722,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lechuga</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -8952,12 +9746,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Especias fajita</t>
+          <t>Queso rallado</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -8976,12 +9770,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Nata agria</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9000,12 +9794,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Guacamole</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9019,17 +9813,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Hamburguesas</t>
+          <t>Fajitas</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Carne picada de ternera</t>
+          <t>Lechuga</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9043,17 +9837,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Hamburguesas</t>
+          <t>Fajitas</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pan de hamburguesa</t>
+          <t>Especias fajita</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -9067,17 +9861,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Hamburguesas</t>
+          <t>Fajitas</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Queso en lonchas</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -9091,17 +9885,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Hamburguesas</t>
+          <t>Fajitas</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lechuga</t>
+          <t>Guacamole</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -9120,12 +9914,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>Carne picada de ternera</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>180</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -9144,12 +9938,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Cebolla</t>
+          <t>Pan de hamburguesa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -9168,12 +9962,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Bacon</t>
+          <t>Queso en lonchas</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -9192,12 +9986,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pepinillos</t>
+          <t>Lechuga</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -9216,12 +10010,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ketchup</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -9240,12 +10034,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mostaza</t>
+          <t>Cebolla</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -9264,12 +10058,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mayonesa</t>
+          <t>Bacon</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -9288,12 +10082,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Patatas congeladas</t>
+          <t>Pepinillos</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -9307,17 +10101,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Pizzas</t>
+          <t>Hamburguesas</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Masa de pizza</t>
+          <t>Ketchup</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -9331,17 +10125,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Pizzas</t>
+          <t>Hamburguesas</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tomate natural</t>
+          <t>Mostaza</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -9355,17 +10149,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Pizzas</t>
+          <t>Hamburguesas</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Mozzarella</t>
+          <t>Mayonesa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -9379,17 +10173,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pizzas</t>
+          <t>Hamburguesas</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Jamon cocido</t>
+          <t>Patatas congeladas</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -9408,12 +10202,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Salami/pepperoni</t>
+          <t>Masa de pizza</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -9432,12 +10226,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Champinones</t>
+          <t>Tomate natural</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -9456,12 +10250,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Pimiento rojo</t>
+          <t>Mozzarella</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -9480,12 +10274,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Aceitunas negras</t>
+          <t>Jamon cocido</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -9504,12 +10298,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Oregano</t>
+          <t>Salami/pepperoni</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -9528,12 +10322,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Champinones</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -9547,29 +10341,21 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Fritura de pescado</t>
+          <t>Pizzas</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Boquerones</t>
+          <t>Pimiento rojo</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Pescado</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>No</t>
@@ -9579,29 +10365,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fritura de pescado</t>
+          <t>Pizzas</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Calamar</t>
+          <t>Aceitunas negras</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Pescado</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>No</t>
@@ -9611,29 +10389,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Fritura de pescado</t>
+          <t>Pizzas</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rosada</t>
+          <t>Oregano</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Pescado</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>No</t>
@@ -9643,29 +10413,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Fritura de pescado</t>
+          <t>Pizzas</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cazon</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Pescado</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>No</t>
@@ -9680,16 +10442,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Harina de freir</t>
+          <t>Boquerones</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>No</t>
@@ -9704,7 +10474,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Aceite de girasol</t>
+          <t>Calamar</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9712,8 +10482,16 @@
           <t>80</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>No</t>
@@ -9728,16 +10506,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Limon</t>
+          <t>Rosada</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>No</t>
@@ -9752,16 +10538,24 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sal</t>
+          <t>Cazon</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>No</t>
@@ -9776,12 +10570,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Perejil</t>
+          <t>Harina de freir</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -9800,12 +10594,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Vinagre</t>
+          <t>Aceite de girasol</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -9824,12 +10618,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Pimenton</t>
+          <t>Limon</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -9848,12 +10642,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Comino</t>
+          <t>Sal</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -9872,12 +10666,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ajo</t>
+          <t>Perejil</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -9896,17 +10690,497 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Oregano</t>
+          <t>Vinagre</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Fritura de pescado</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Pimenton</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Fritura de pescado</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Comino</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Fritura de pescado</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Ajo</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Fritura de pescado</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Oregano</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Arroz</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Gambas/langostinos</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Mejillones</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Calamar</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Almejas</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Caldo de pescado</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Tomate natural</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cebolla</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pimiento rojo</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ajo</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Guisantes</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Aceite de oliva</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pimenton</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Azafran</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Limon</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Paella de marisco</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/data/CompraSanJose.xlsx
+++ b/data/CompraSanJose.xlsx
@@ -3248,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3269,15 +3269,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>PasosPrevios</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Preparacion</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -3300,6 +3305,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Descongela la aguja de vaca la noche antes en la nevera.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>1. Pica pimiento verde, ajos y tomate. En la paellera, sofrie pimiento y ajos; anade la aguja de vaca troceada y el chorizo salpimentados y dora.
 2. Incorpora el tomate natural y rehoga.
@@ -3309,12 +3319,12 @@
 6. Apaga, tapa con un pano y reposa 7-8 min.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-arroces/receta-arroz-campero-tipico-andalucia</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3333,6 +3343,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>Con antelacion: lava las laminas de berenjena con agua y sal y dejalas 30-45 min para quitar el amargor; escurre y seca. Hornea o frie las laminas de patata y de berenjena antes de montar. Necesitas papel vegetal de horno.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>1. Lamina las berenjenas, salalas y dejalas sudar; frielas ligeramente y reserva.
 2. Corta las patatas en rodajas y frielas ligeramente para la base.
@@ -3343,12 +3358,12 @@
 7. Hornea 20 min a 160C y gratina 3 min a 220C.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-carnes-y-aves/moussaka-receta-griega</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Con ternera (no cordero); tomate tamizado.</t>
         </is>
@@ -3371,6 +3386,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>La noche anterior: deja los garbanzos en remojo (o usa garbanzos ya cocidos). Puedes guisar la carrillera la vispera; gana de un dia para otro.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>1. Trocea la carrillera de ternera, salpimienta y dorala a fuego alto en la cazuela.
 2. Baja el fuego, anade cebolla y pocha 10 min.
@@ -3381,12 +3401,12 @@
 7. Sirve la semola de base y reparte el guiso por encima.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://www.todosacomer.net/recetas/guisos-pasta-arroces/cuscus-con-verduras-y-pollo</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Zanahoria opcional; tomate tamizado (poco).</t>
         </is>
@@ -3408,7 +3428,8 @@
           <t>Paco</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>1. Corta las patatas en rodajas de 1/2 cm; pica ajo y corta cebolla y pimiento verde.
 2. En abundante aceite, frie ajo y luego patatas, cebolla y pimiento; 5 min a fuego fuerte.
@@ -3418,12 +3439,12 @@
 6. Emplata: base de patatas, encima embutidos, huevos fritos y unas lonchas de jamon.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://bonviveur.com/es/recetas/plato-alpujarreno</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Patatas a lo pobre + embutido + huevos.</t>
         </is>
@@ -3446,6 +3467,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>Preparalo con antelacion y enfrialo en nevera al menos 2 h antes de servir.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>1. Tritura los tomates (1 kg por cada 6 raciones); no hace falta pelar ni despepitar.
 2. Anade el pan (unos 200 g de telera por cada 6) y deja que se empape 10 min.
@@ -3455,12 +3481,12 @@
 6. De acompanamiento, salpimienta los filetes y hazlos a la plancha 2-3 min por cara.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-sopas-y-cremas/receta-de-salmorejo-cordobes-tradicional</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Acompanamiento elegible; por defecto filetes de ternera.</t>
         </is>
@@ -3482,7 +3508,8 @@
           <t>Manolo</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>1. Corta pan candeal asentado en cubos de 1 cm; humedecelo con agua salada, tapa con un pano y reposa (mejor de un dia para otro).
 2. Frie el chorizo en rodajas y la panceta en dados hasta que suelten grasa; reserva.
@@ -3492,12 +3519,12 @@
 6. Para grupo grande, trabaja por tandas o en perol amplio; sirve muy caliente.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-tradicionales/mejor-receta-migas-pan-chorizo-clasico-potente-como-tradicional</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3516,6 +3543,11 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>Se puede cocinar la vispera; gana de un dia para otro.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>1. Pocha la cebolla en aceite hasta transparente.
 2. Anade ajo, pimenton picante y comino; rehoga.
@@ -3525,12 +3557,12 @@
 6. Rectifica de sal y picante; sirve con arroz blanco y nachos.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-carnes-y-aves/chili-receta-mexicana-con-y-sin-thermomix</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Con guarnicion de arroz.</t>
         </is>
@@ -3553,6 +3585,11 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>Precalienta el horno a 180C. Cubre la bandeja con papel vegetal o engrasala bien.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>1. Precalienta el horno a 180C. Mezcla sal, pimienta y tomillo/romero.
 2. Parte las patatas, hazles cortes y colocalas en la bandeja engrasada.
@@ -3562,12 +3599,12 @@
 6. Trincha, riega con la salsa y sirve; para mas comensales reparte en varias bandejas sin amontonar.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://www.hogarmania.com/cocina/recetas/carnes/pollo-asado-patatas-ensalada-verde-16651.html</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>El 'asado de carne/pescado'.</t>
         </is>
@@ -3589,7 +3626,8 @@
           <t>Paco</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>1. Pica en cuadraditos la cebolla y el pimiento verde; pica una pizca de ajo.
 2. Pocha cebolla, pimiento y ajo en aceite 10-15 min a fuego medio.
@@ -3599,12 +3637,12 @@
 6. Sirve el pisto con los huevos fritos por encima.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-legumbres-y-verduras/pisto-de-pimientos-y-tomates-la-receta-de-mi-abuela</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>RESPALDO: solo cebolla, tomate frito y pimiento verde + huevos.</t>
         </is>
@@ -3627,6 +3665,11 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>Enciende las brasas 30-40 min antes (carbon + pastillas). Ten la carne fresca (sin congelar) y las salsas listas.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>1. Enciende la barbacoa 30-40 min antes; espera a que las brasas esten blanquecinas, sin llama.
 2. Reparte el carbon para calor uniforme; parrilla no muy pegada a las brasas.
@@ -3637,12 +3680,12 @@
 7. NO sales antes: echa la sal SOLO AL FINAL, en el plato.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/cultura-gastronomica/los-9-trucos-imprescindibles-para-convertirte-en-el-maestro-de-las-barbacoas</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Cerdo y embutido. Tope de carne por comensal (RF-26).</t>
         </is>
@@ -3665,6 +3708,11 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>Enciende las brasas 30-40 min antes. Saca el vacuno de la nevera para atemperar. Ten el chimichurri preparado.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>1. Enciende las brasas 30-40 min antes; saca el vacuno de la nevera para atemperar.
 2. Sella el entrecot y el chuleton sobre brasa fuerte ~5 min por cara; una sola vuelta.
@@ -3675,12 +3723,12 @@
 7. Echa la sal AL FINAL para no resecar la carne.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetario/83-mejores-recetas-barbacoa-para-sacar-todo-partido-a-parrilla-este-verano</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Vacuno, pollo y verdura. Tope de carne por comensal (RF-26).</t>
         </is>
@@ -3702,7 +3750,8 @@
           <t>Manolo</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>1. Corta el pollo en tiras y la cebolla y los pimientos en tiras anchas.
 2. Salpimienta el pollo y saltealo en aceite muy caliente; reserva.
@@ -3712,12 +3761,12 @@
 6. Rellena y enrolla; sirve con guacamole, nata agria, queso, tomate y lechuga.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://www.divinacocina.es/fajitas-de-pollo-faciles/</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3731,7 +3780,8 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>1. Usa carne picada fresca; salpimienta.
 2. Mezcla sin amasar en exceso y forma discos regulares.
@@ -3742,12 +3792,12 @@
 7. Monta: pan, lechuga y tomate, hamburguesa, bacon, cebolla y pepinillos, salsa y cierra. Acompana con patatas.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-carnes-y-aves/como-hacer-hamburguesas-caseras</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3761,7 +3811,8 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>1. Mezcla la masa (harina, agua, levadura, sal, aceite) hasta homogenea; reposa 1-3 h.
 2. Divide, bolea y deja reposar; sacala 1-2 h antes si estaba en frio.
@@ -3772,12 +3823,12 @@
 7. Reposa unos minutos; anade oregano y aceite al salir.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-panes/pizza-casera-la-guia-definitiva</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3796,6 +3847,11 @@
         </is>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>El dia anterior: adoba el cazon y la rosada (ajo, comino, oregano, pimenton, vinagre de Jerez, laurel y sal) y macera en nevera 8-12 h. Saca a temperatura antes de enharinar.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>1. Adobo del cazon: maja ajo, comino, oregano y pimenton, anade vinagre, laurel y sal.
 2. Corta el cazon en tacos, cubrelo con el adobo y macera en nevera 8 h (mejor toda la noche).
@@ -3806,12 +3862,12 @@
 7. Escurre en papel y sirve al momento con limon.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://www.directoalpaladar.com/recetas-de-aperitivos/como-se-hace-el-cazon-en-adobo-receta-de-bienmesabe</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Surtido elegible; incluye adobo y tempura.</t>
         </is>
@@ -3833,7 +3889,8 @@
           <t>Paco</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>1. Sofrie cebolla, pimiento y ajo en aceite; anade tomate natural.
 2. Rehoga el arroz con pimenton y azafran.
@@ -3842,8 +3899,8 @@
 5. Cuece 18 min sin remover; reposa 5 min. Sirve con limon.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Opcion alternativa de arroz.</t>
         </is>
@@ -11869,7 +11926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12461,6 +12518,116 @@
         </is>
       </c>
       <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Papel vegetal de horno</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rollo</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Papel de aluminio</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rollo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Carbon para barbacoa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Saco</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Pastillas de encendido</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Caja</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Bolsas de congelacion</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Caja</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
